--- a/moduli_aziende/aifecs/moduli_compilati/MOD-740-B-Monitoraggio_Comunicazione.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-740-B-Monitoraggio_Comunicazione.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b8dd52cc5d748be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf836dc69294241da"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -422,7 +405,7 @@
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="7"/>
       <x:c r="B2" s="8" t="str">
-        <x:v>Canale ufficiale rete da confermare</x:v>
+        <x:v>Canale ufficiale della rete</x:v>
       </x:c>
       <x:c r="C2" s="8" t="str">
         <x:v>Aggiornamenti requisiti e istruzioni operative</x:v>
@@ -436,9 +419,7 @@
       <x:c r="F2" s="8" t="str">
         <x:v>Riscontro comunicazioni critiche</x:v>
       </x:c>
-      <x:c r="G2" s="8" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G2" s="8"/>
     </x:row>
     <x:row r="3" ht="50" customHeight="1">
       <x:c r="A3" s="7"/>
@@ -457,9 +438,7 @@
       <x:c r="F3" s="8" t="str">
         <x:v>Verifica comprensione e richieste</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G3" s="8"/>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="7"/>
@@ -478,9 +457,7 @@
       <x:c r="F4" s="8" t="str">
         <x:v>Azioni con responsabilità e scadenze</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G4" s="8"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3"/>
@@ -520,6 +497,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R618464cf48eb4011"/>
 </x:worksheet>
 </file>